--- a/Exam/gymtrackerpro/lib/repository/__tests__/bbt/user-repository/updateAdmin-bbt-form.xlsx
+++ b/Exam/gymtrackerpro/lib/repository/__tests__/bbt/user-repository/updateAdmin-bbt-form.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="94">
   <si>
     <t>Statement: UserRepository.updateAdmin(adminId, data) – atomically updates Admin and User.</t>
   </si>
@@ -154,76 +154,58 @@
     <t>adminId = ""</t>
   </si>
   <si>
+    <t>adminId = "a" (inex)</t>
+  </si>
+  <si>
+    <t>adminId = "a" (exist)</t>
+  </si>
+  <si>
+    <t>Email field</t>
+  </si>
+  <si>
+    <t>email = undefined/empty/char</t>
+  </si>
+  <si>
+    <t>FullName field</t>
+  </si>
+  <si>
+    <t>fullName = undefined/empty/char</t>
+  </si>
+  <si>
+    <t>Phone field</t>
+  </si>
+  <si>
+    <t>phone = undefined/empty/char</t>
+  </si>
+  <si>
+    <t>DOB field</t>
+  </si>
+  <si>
+    <t>dateOfBirth = undefined/empty/char</t>
+  </si>
+  <si>
+    <t>Password field</t>
+  </si>
+  <si>
+    <t>password = undefined/empty/char</t>
+  </si>
+  <si>
+    <t>BVA</t>
+  </si>
+  <si>
+    <t>BVA-1 EmptyID</t>
+  </si>
+  <si>
+    <t>BVA-2 InexCharID</t>
+  </si>
+  <si>
     <t>adminId = "a"</t>
   </si>
   <si>
-    <t>Email field</t>
-  </si>
-  <si>
-    <t>email = undefined</t>
-  </si>
-  <si>
-    <t>email = ""</t>
-  </si>
-  <si>
-    <t>email = "a"</t>
-  </si>
-  <si>
-    <t>FullName field</t>
-  </si>
-  <si>
-    <t>fullName = undefined</t>
-  </si>
-  <si>
-    <t>fullName = ""</t>
-  </si>
-  <si>
-    <t>fullName = "A"</t>
-  </si>
-  <si>
-    <t>Phone field</t>
-  </si>
-  <si>
-    <t>phone = undefined</t>
-  </si>
-  <si>
-    <t>phone = ""</t>
-  </si>
-  <si>
-    <t>phone = "a"</t>
-  </si>
-  <si>
-    <t>DOB field</t>
-  </si>
-  <si>
-    <t>dateOfBirth = undefined</t>
-  </si>
-  <si>
-    <t>dateOfBirth = ""</t>
-  </si>
-  <si>
-    <t>dateOfBirth = "a"</t>
-  </si>
-  <si>
-    <t>Password field</t>
-  </si>
-  <si>
-    <t>password = undefined</t>
-  </si>
-  <si>
-    <t>password = ""</t>
-  </si>
-  <si>
-    <t>password = "a"</t>
-  </si>
-  <si>
-    <t>BVA</t>
-  </si>
-  <si>
-    <t>BVA-1 EmptyID</t>
-  </si>
-  <si>
-    <t>BVA-2 OneCharID</t>
+    <t>BVA-3 ExistCharID</t>
+  </si>
+  <si>
+    <t>Updates successfully</t>
   </si>
   <si>
     <t>TC from EC</t>
@@ -274,49 +256,7 @@
     <t>BVA-3</t>
   </si>
   <si>
-    <t>Returns items</t>
-  </si>
-  <si>
-    <t>BVA-4</t>
-  </si>
-  <si>
-    <t>BVA-5</t>
-  </si>
-  <si>
-    <t>BVA-6</t>
-  </si>
-  <si>
-    <t>BVA-7</t>
-  </si>
-  <si>
-    <t>BVA-8</t>
-  </si>
-  <si>
-    <t>BVA-9</t>
-  </si>
-  <si>
-    <t>BVA-10</t>
-  </si>
-  <si>
-    <t>BVA-11</t>
-  </si>
-  <si>
-    <t>BVA-12</t>
-  </si>
-  <si>
-    <t>BVA-13</t>
-  </si>
-  <si>
-    <t>BVA-14</t>
-  </si>
-  <si>
-    <t>BVA-15</t>
-  </si>
-  <si>
-    <t>BVA-16</t>
-  </si>
-  <si>
-    <t>BVA-17</t>
+    <t>Various field updates</t>
   </si>
   <si>
     <t>Testing</t>
@@ -1091,7 +1031,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -1137,10 +1077,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>46</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -1148,7 +1088,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>1</v>
+        <v>47</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>48</v>
@@ -1159,10 +1099,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>1</v>
+        <v>49</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -1170,10 +1110,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -1181,10 +1121,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>1</v>
+        <v>53</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -1192,109 +1132,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>1</v>
+        <v>55</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="10" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="1">
-        <v>9</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="11" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="1">
-        <v>10</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C11" s="1" t="s">
         <v>56</v>
-      </c>
-    </row>
-    <row r="12" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="1">
-        <v>11</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="13" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="1">
-        <v>12</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="14" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="1">
-        <v>13</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="15" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="1">
-        <v>14</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="16" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="1">
-        <v>15</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="17" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="1">
-        <v>16</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="18" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="1">
-        <v>17</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -1305,7 +1146,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -1320,7 +1161,7 @@
         <v>24</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="C1" s="4" t="s">
         <v>26</v>
@@ -1337,7 +1178,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>44</v>
@@ -1354,15 +1195,32 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>35</v>
       </c>
       <c r="E3" s="5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E4" s="5" t="s">
         <v>32</v>
       </c>
     </row>
@@ -1374,7 +1232,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -1390,10 +1248,10 @@
         <v>24</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="D1" s="4" t="s">
         <v>26</v>
@@ -1410,16 +1268,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="F2" s="5" t="s">
         <v>32</v>
@@ -1456,7 +1314,7 @@
         <v>1</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>37</v>
@@ -1470,16 +1328,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="F5" s="5" t="s">
         <v>32</v>
@@ -1490,16 +1348,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="F6" s="5" t="s">
         <v>32</v>
@@ -1516,7 +1374,7 @@
         <v>1</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>40</v>
@@ -1533,7 +1391,7 @@
         <v>1</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>44</v>
@@ -1553,7 +1411,7 @@
         <v>1</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>45</v>
@@ -1573,13 +1431,13 @@
         <v>1</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>85</v>
+        <v>22</v>
       </c>
       <c r="F10" s="5" t="s">
         <v>32</v>
@@ -1593,13 +1451,13 @@
         <v>1</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>86</v>
+        <v>57</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>48</v>
+        <v>79</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>85</v>
+        <v>22</v>
       </c>
       <c r="F11" s="5" t="s">
         <v>32</v>
@@ -1613,13 +1471,13 @@
         <v>1</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>87</v>
+        <v>57</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>49</v>
+        <v>79</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>85</v>
+        <v>22</v>
       </c>
       <c r="F12" s="5" t="s">
         <v>32</v>
@@ -1633,13 +1491,13 @@
         <v>1</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>88</v>
+        <v>57</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>51</v>
+        <v>79</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>85</v>
+        <v>22</v>
       </c>
       <c r="F13" s="5" t="s">
         <v>32</v>
@@ -1653,13 +1511,13 @@
         <v>1</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>89</v>
+        <v>57</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>52</v>
+        <v>79</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>85</v>
+        <v>22</v>
       </c>
       <c r="F14" s="5" t="s">
         <v>32</v>
@@ -1673,13 +1531,13 @@
         <v>1</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>90</v>
+        <v>57</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>85</v>
+        <v>22</v>
       </c>
       <c r="F15" s="5" t="s">
         <v>32</v>
@@ -1693,13 +1551,13 @@
         <v>1</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>91</v>
+        <v>57</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>55</v>
+        <v>79</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>85</v>
+        <v>22</v>
       </c>
       <c r="F16" s="5" t="s">
         <v>32</v>
@@ -1713,13 +1571,13 @@
         <v>1</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>92</v>
+        <v>57</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>85</v>
+        <v>22</v>
       </c>
       <c r="F17" s="5" t="s">
         <v>32</v>
@@ -1733,13 +1591,13 @@
         <v>1</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>93</v>
+        <v>57</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>85</v>
+        <v>22</v>
       </c>
       <c r="F18" s="5" t="s">
         <v>32</v>
@@ -1753,13 +1611,13 @@
         <v>1</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>94</v>
+        <v>57</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>59</v>
+        <v>79</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>85</v>
+        <v>22</v>
       </c>
       <c r="F19" s="5" t="s">
         <v>32</v>
@@ -1773,13 +1631,13 @@
         <v>1</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>95</v>
+        <v>57</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>60</v>
+        <v>79</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>85</v>
+        <v>22</v>
       </c>
       <c r="F20" s="5" t="s">
         <v>32</v>
@@ -1793,13 +1651,13 @@
         <v>1</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>96</v>
+        <v>57</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>85</v>
+        <v>22</v>
       </c>
       <c r="F21" s="5" t="s">
         <v>32</v>
@@ -1813,13 +1671,13 @@
         <v>1</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>97</v>
+        <v>57</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>85</v>
+        <v>22</v>
       </c>
       <c r="F22" s="5" t="s">
         <v>32</v>
@@ -1833,13 +1691,13 @@
         <v>1</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>98</v>
+        <v>57</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>85</v>
+        <v>22</v>
       </c>
       <c r="F23" s="5" t="s">
         <v>32</v>
@@ -1853,15 +1711,35 @@
         <v>1</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>99</v>
+        <v>57</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>65</v>
+        <v>79</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>85</v>
+        <v>22</v>
       </c>
       <c r="F24" s="5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="25" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="1">
+        <v>24</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F25" s="5" t="s">
         <v>32</v>
       </c>
     </row>
@@ -1890,16 +1768,16 @@
         <v>1</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2" t="s">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
@@ -1907,45 +1785,45 @@
     </row>
     <row r="2" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>103</v>
+        <v>83</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>104</v>
+        <v>84</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>105</v>
+        <v>85</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>107</v>
+        <v>87</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>108</v>
+        <v>88</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>109</v>
+        <v>89</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>104</v>
+        <v>84</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>105</v>
+        <v>85</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="B3" s="1">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C3" s="1">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D3" s="1">
         <v>0</v>
@@ -1954,19 +1832,19 @@
         <v>0</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>111</v>
+        <v>91</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>112</v>
+        <v>92</v>
       </c>
       <c r="H3" s="1">
         <v>0</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>113</v>
+        <v>93</v>
       </c>
     </row>
   </sheetData>

--- a/Exam/gymtrackerpro/lib/repository/__tests__/bbt/user-repository/updateAdmin-bbt-form.xlsx
+++ b/Exam/gymtrackerpro/lib/repository/__tests__/bbt/user-repository/updateAdmin-bbt-form.xlsx
@@ -17,9 +17,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="94">
-  <si>
-    <t>Statement: UserRepository.updateAdmin(adminId, data) – atomically updates Admin and User.</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="123">
+  <si>
+    <t>Statement: UserRepository.updateAdmin(id, data) – Updates an admin and their user record. Returns the updated AdminWithUser on success. Throws NotFoundError if the admin does not exist. Throws ConflictError if the new email is already taken by another user. Throws TransactionError if the database write fails.</t>
   </si>
   <si>
     <t/>
@@ -31,13 +31,13 @@
     <t>Data</t>
   </si>
   <si>
-    <t>Input: adminId: string, data: UpdateAdminInput</t>
+    <t>Input: id: string, data: UpdateAdminInput { fullName?, email?, phone?, dateOfBirth?, password? }</t>
   </si>
   <si>
     <t>precondition</t>
   </si>
   <si>
-    <t>Database is accessible</t>
+    <t>Database is accessible. An admin with the given ID may or may not exist. Any new email may or may not already be registered to another user.</t>
   </si>
   <si>
     <t>Results</t>
@@ -49,7 +49,7 @@
     <t>postcondition</t>
   </si>
   <si>
-    <t>Updates records or throws error.</t>
+    <t>On success: AdminWithUser returned with updated fields (result.user.fullName, result.id). On failure: NotFoundError, ConflictError, or TransactionError thrown.</t>
   </si>
   <si>
     <t>Number EC</t>
@@ -67,28 +67,37 @@
     <t>Admin existence</t>
   </si>
   <si>
-    <t>Found</t>
-  </si>
-  <si>
-    <t>Not found (NotFoundError)</t>
-  </si>
-  <si>
-    <t>Email conflict</t>
-  </si>
-  <si>
-    <t>New email unique or same</t>
-  </si>
-  <si>
-    <t>New email taken (ConflictError)</t>
+    <t>Existing ID + valid data → AdminWithUser returned with result.user.fullName: "Updated Admin"</t>
+  </si>
+  <si>
+    <t>Non-existent ID → NotFoundError</t>
+  </si>
+  <si>
+    <t>Email uniqueness</t>
+  </si>
+  <si>
+    <t>New email not taken → AdminWithUser returned</t>
+  </si>
+  <si>
+    <t>New email taken by another user → ConflictError</t>
+  </si>
+  <si>
+    <t>Email identity</t>
+  </si>
+  <si>
+    <t>Same email as current user → AdminWithUser returned with result.id: ADMIN_ID</t>
+  </si>
+  <si>
+    <t>Password change</t>
+  </si>
+  <si>
+    <t>New password provided → AdminWithUser returned with result.id: ADMIN_ID</t>
   </si>
   <si>
     <t>Database write</t>
   </si>
   <si>
-    <t>Success</t>
-  </si>
-  <si>
-    <t>Failure (TransactionError)</t>
+    <t>Write fails → TransactionError</t>
   </si>
   <si>
     <t>No TC</t>
@@ -106,13 +115,13 @@
     <t>Actual Result</t>
   </si>
   <si>
-    <t>EC-1, EC-3, EC-5</t>
-  </si>
-  <si>
-    <t>Existing admin, valid data</t>
-  </si>
-  <si>
-    <t>Returns updated AdminWithUser</t>
+    <t>EC-1</t>
+  </si>
+  <si>
+    <t>id: ADMIN_ID, data: { fullName: "Updated Admin" }</t>
+  </si>
+  <si>
+    <t>AdminWithUser returned with result.user.fullName: "Updated Admin"</t>
   </si>
   <si>
     <t>Passed</t>
@@ -121,25 +130,43 @@
     <t>EC-2</t>
   </si>
   <si>
-    <t>Non-existent adminId</t>
-  </si>
-  <si>
-    <t>Throws NotFoundError</t>
+    <t>id: NONEXISTENT_ID, data: { fullName: "Name" }</t>
+  </si>
+  <si>
+    <t>throws NotFoundError</t>
   </si>
   <si>
     <t>EC-4</t>
   </si>
   <si>
-    <t>Throws ConflictError</t>
+    <t>id: ADMIN_ID, data: { email: "taken@example.com" }</t>
+  </si>
+  <si>
+    <t>throws ConflictError</t>
+  </si>
+  <si>
+    <t>EC-5</t>
+  </si>
+  <si>
+    <t>id: ADMIN_ID, data: { email: MOCK_ADMIN_WITH_USER.user.email }</t>
+  </si>
+  <si>
+    <t>AdminWithUser returned with result.id: ADMIN_ID</t>
   </si>
   <si>
     <t>EC-6</t>
   </si>
   <si>
-    <t>Database failure</t>
-  </si>
-  <si>
-    <t>Throws TransactionError</t>
+    <t>id: ADMIN_ID, data: { password: "NewAdminPass1!" }</t>
+  </si>
+  <si>
+    <t>EC-7</t>
+  </si>
+  <si>
+    <t>id: ADMIN_ID, data: { fullName: "New Name" }, DB fails</t>
+  </si>
+  <si>
+    <t>throws TransactionError</t>
   </si>
   <si>
     <t>Number BVA</t>
@@ -148,64 +175,151 @@
     <t>BVA Test Case</t>
   </si>
   <si>
-    <t>ID length</t>
-  </si>
-  <si>
-    <t>adminId = ""</t>
-  </si>
-  <si>
-    <t>adminId = "a" (inex)</t>
-  </si>
-  <si>
-    <t>adminId = "a" (exist)</t>
-  </si>
-  <si>
-    <t>Email field</t>
-  </si>
-  <si>
-    <t>email = undefined/empty/char</t>
-  </si>
-  <si>
-    <t>FullName field</t>
-  </si>
-  <si>
-    <t>fullName = undefined/empty/char</t>
-  </si>
-  <si>
-    <t>Phone field</t>
-  </si>
-  <si>
-    <t>phone = undefined/empty/char</t>
-  </si>
-  <si>
-    <t>DOB field</t>
-  </si>
-  <si>
-    <t>dateOfBirth = undefined/empty/char</t>
-  </si>
-  <si>
-    <t>Password field</t>
-  </si>
-  <si>
-    <t>password = undefined/empty/char</t>
+    <t>Admin ID length</t>
+  </si>
+  <si>
+    <t>0 chars (empty, not found), 1 char (not found), 1 char (found)</t>
+  </si>
+  <si>
+    <t>email field</t>
+  </si>
+  <si>
+    <t>email: undefined, email: "" (empty), email: "a" (one char)</t>
+  </si>
+  <si>
+    <t>fullName field</t>
+  </si>
+  <si>
+    <t>fullName: undefined, fullName: "" (empty), fullName: "A" (one char)</t>
+  </si>
+  <si>
+    <t>phone field</t>
+  </si>
+  <si>
+    <t>phone: undefined, phone: "" (empty), phone: "a" (one char)</t>
+  </si>
+  <si>
+    <t>dateOfBirth field</t>
+  </si>
+  <si>
+    <t>dateOfBirth: undefined, dateOfBirth: "" (empty), dateOfBirth: "a" (one char)</t>
+  </si>
+  <si>
+    <t>password field</t>
+  </si>
+  <si>
+    <t>password: undefined, password: "" (empty), password: "a" (one char)</t>
   </si>
   <si>
     <t>BVA</t>
   </si>
   <si>
-    <t>BVA-1 EmptyID</t>
-  </si>
-  <si>
-    <t>BVA-2 InexCharID</t>
-  </si>
-  <si>
-    <t>adminId = "a"</t>
-  </si>
-  <si>
-    <t>BVA-3 ExistCharID</t>
-  </si>
-  <si>
-    <t>Updates successfully</t>
+    <t>BVA-1 (n=0)</t>
+  </si>
+  <si>
+    <t>id: "", data: { fullName: "New Name" }</t>
+  </si>
+  <si>
+    <t>BVA-1 (n=1)</t>
+  </si>
+  <si>
+    <t>id: "a" (no match), data: { fullName: "New Name" }</t>
+  </si>
+  <si>
+    <t>id: "a" (found), data: { fullName: "New Name" }</t>
+  </si>
+  <si>
+    <t>AdminWithUser returned with result.id: "a"</t>
+  </si>
+  <si>
+    <t>BVA-2 (undef)</t>
+  </si>
+  <si>
+    <t>id: ADMIN_ID, data: { email: undefined }</t>
+  </si>
+  <si>
+    <t>BVA-2 (n=0)</t>
+  </si>
+  <si>
+    <t>id: ADMIN_ID, data: { email: "" }</t>
+  </si>
+  <si>
+    <t>BVA-2 (n=1)</t>
+  </si>
+  <si>
+    <t>id: ADMIN_ID, data: { email: "a" }</t>
+  </si>
+  <si>
+    <t>BVA-3 (undef)</t>
+  </si>
+  <si>
+    <t>id: ADMIN_ID, data: { fullName: undefined }</t>
+  </si>
+  <si>
+    <t>BVA-3 (n=0)</t>
+  </si>
+  <si>
+    <t>id: ADMIN_ID, data: { fullName: "" }</t>
+  </si>
+  <si>
+    <t>BVA-3 (n=1)</t>
+  </si>
+  <si>
+    <t>id: ADMIN_ID, data: { fullName: "A" }</t>
+  </si>
+  <si>
+    <t>BVA-4 (undef)</t>
+  </si>
+  <si>
+    <t>id: ADMIN_ID, data: { phone: undefined }</t>
+  </si>
+  <si>
+    <t>BVA-4 (n=0)</t>
+  </si>
+  <si>
+    <t>id: ADMIN_ID, data: { phone: "" }</t>
+  </si>
+  <si>
+    <t>BVA-4 (n=1)</t>
+  </si>
+  <si>
+    <t>id: ADMIN_ID, data: { phone: "a" }</t>
+  </si>
+  <si>
+    <t>BVA-5 (undef)</t>
+  </si>
+  <si>
+    <t>id: ADMIN_ID, data: { dateOfBirth: undefined }</t>
+  </si>
+  <si>
+    <t>BVA-5 (n=0)</t>
+  </si>
+  <si>
+    <t>id: ADMIN_ID, data: { dateOfBirth: "" }</t>
+  </si>
+  <si>
+    <t>BVA-5 (n=1)</t>
+  </si>
+  <si>
+    <t>id: ADMIN_ID, data: { dateOfBirth: "a" }</t>
+  </si>
+  <si>
+    <t>BVA-6 (undef)</t>
+  </si>
+  <si>
+    <t>id: ADMIN_ID, data: { password: undefined }</t>
+  </si>
+  <si>
+    <t>BVA-6 (n=0)</t>
+  </si>
+  <si>
+    <t>id: ADMIN_ID, data: { password: "" }</t>
+  </si>
+  <si>
+    <t>BVA-6 (n=1)</t>
+  </si>
+  <si>
+    <t>id: ADMIN_ID, data: { password: "a" }</t>
   </si>
   <si>
     <t>TC from EC</t>
@@ -214,39 +328,6 @@
     <t>TC from BVA</t>
   </si>
   <si>
-    <t>EC-1</t>
-  </si>
-  <si>
-    <t>Existing admin, update fullName</t>
-  </si>
-  <si>
-    <t>Admin record updated</t>
-  </si>
-  <si>
-    <t>Email taken by other user</t>
-  </si>
-  <si>
-    <t>EC-3</t>
-  </si>
-  <si>
-    <t>Update to current email</t>
-  </si>
-  <si>
-    <t>Skips conflict check</t>
-  </si>
-  <si>
-    <t>EC-5</t>
-  </si>
-  <si>
-    <t>Update with new password</t>
-  </si>
-  <si>
-    <t>Password is hashed</t>
-  </si>
-  <si>
-    <t>Database write error</t>
-  </si>
-  <si>
     <t>BVA-1</t>
   </si>
   <si>
@@ -256,7 +337,13 @@
     <t>BVA-3</t>
   </si>
   <si>
-    <t>Various field updates</t>
+    <t>BVA-4</t>
+  </si>
+  <si>
+    <t>BVA-5</t>
+  </si>
+  <si>
+    <t>BVA-6</t>
   </si>
   <si>
     <t>Testing</t>
@@ -289,7 +376,7 @@
     <t>Re-tested</t>
   </si>
   <si>
-    <t>AUTH-06</t>
+    <t>REPO-11</t>
   </si>
   <si>
     <t>n/a</t>
@@ -814,7 +901,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -855,7 +942,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>1</v>
@@ -883,7 +970,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>1</v>
@@ -911,13 +998,27 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>23</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -928,7 +1029,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -940,19 +1041,19 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -960,16 +1061,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -977,16 +1078,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -994,16 +1095,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1011,16 +1112,50 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>32</v>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -1031,7 +1166,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -1041,13 +1176,13 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
     </row>
     <row r="2" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -1055,10 +1190,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -1066,10 +1201,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>1</v>
+        <v>54</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
     </row>
     <row r="4" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -1077,10 +1212,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>1</v>
+        <v>56</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -1088,10 +1223,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>48</v>
+        <v>59</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -1099,10 +1234,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -1110,32 +1245,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="8" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="1">
-        <v>7</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="9" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="1">
-        <v>8</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
     </row>
   </sheetData>
@@ -1146,7 +1259,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -1158,19 +1271,19 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1178,16 +1291,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>44</v>
+        <v>66</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1195,16 +1308,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1212,16 +1325,271 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>32</v>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <v>11</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <v>12</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
+        <v>13</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
+        <v>14</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="16" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
+        <v>15</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="17" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="1">
+        <v>16</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="18" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="1">
+        <v>17</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="19" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="1">
+        <v>18</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -1245,22 +1613,22 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>63</v>
+        <v>101</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>64</v>
+        <v>102</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1268,19 +1636,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>65</v>
+        <v>32</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>66</v>
+        <v>33</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>67</v>
+        <v>34</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1288,19 +1656,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1308,19 +1676,19 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>68</v>
+        <v>40</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1328,19 +1696,19 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>69</v>
+        <v>42</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>70</v>
+        <v>43</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>71</v>
+        <v>44</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1348,19 +1716,19 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>72</v>
+        <v>45</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>73</v>
+        <v>46</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>74</v>
+        <v>44</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1368,19 +1736,19 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>75</v>
+        <v>48</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1391,16 +1759,16 @@
         <v>1</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>76</v>
+        <v>103</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>44</v>
+        <v>66</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1411,16 +1779,16 @@
         <v>1</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>77</v>
+        <v>103</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>45</v>
+        <v>68</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1431,16 +1799,16 @@
         <v>1</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>78</v>
+        <v>103</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>46</v>
+        <v>69</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>22</v>
+        <v>70</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1451,16 +1819,16 @@
         <v>1</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>57</v>
+        <v>104</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1471,16 +1839,16 @@
         <v>1</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>57</v>
+        <v>104</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1491,16 +1859,16 @@
         <v>1</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>57</v>
+        <v>104</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1511,16 +1879,16 @@
         <v>1</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>57</v>
+        <v>105</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1531,16 +1899,16 @@
         <v>1</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>57</v>
+        <v>105</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1551,16 +1919,16 @@
         <v>1</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>57</v>
+        <v>105</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1571,16 +1939,16 @@
         <v>1</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>57</v>
+        <v>106</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="18" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1591,16 +1959,16 @@
         <v>1</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>57</v>
+        <v>106</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="19" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1611,16 +1979,16 @@
         <v>1</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>57</v>
+        <v>106</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="20" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1631,16 +1999,16 @@
         <v>1</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>57</v>
+        <v>107</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="21" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1651,16 +2019,16 @@
         <v>1</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>57</v>
+        <v>107</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="22" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1671,16 +2039,16 @@
         <v>1</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>57</v>
+        <v>107</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>79</v>
+        <v>94</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="23" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1691,16 +2059,16 @@
         <v>1</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>57</v>
+        <v>108</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>79</v>
+        <v>96</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="24" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1711,16 +2079,16 @@
         <v>1</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>57</v>
+        <v>108</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>79</v>
+        <v>98</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="25" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1731,16 +2099,16 @@
         <v>1</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>57</v>
+        <v>108</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -1768,16 +2136,16 @@
         <v>1</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>80</v>
+        <v>109</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2" t="s">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
@@ -1785,39 +2153,39 @@
     </row>
     <row r="2" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>83</v>
+        <v>112</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>84</v>
+        <v>113</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>85</v>
+        <v>114</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>86</v>
+        <v>115</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>87</v>
+        <v>116</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>88</v>
+        <v>117</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>89</v>
+        <v>118</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>84</v>
+        <v>113</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>85</v>
+        <v>114</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>86</v>
+        <v>115</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>90</v>
+        <v>119</v>
       </c>
       <c r="B3" s="1">
         <v>24</v>
@@ -1832,19 +2200,19 @@
         <v>0</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>91</v>
+        <v>120</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>92</v>
+        <v>121</v>
       </c>
       <c r="H3" s="1">
         <v>0</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>93</v>
+        <v>122</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>93</v>
+        <v>122</v>
       </c>
     </row>
   </sheetData>
